--- a/public/exports/66137112.xlsx
+++ b/public/exports/66137112.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M92"/>
+  <dimension ref="A1:O92"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -24,55 +24,65 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ejerskab</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Primær registreret ejer</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Geografisk kommunekode</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t xml:space="preserve">Adresse</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Postnr.</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Energimærkningsfirma</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -91,53 +101,63 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Herstedvestervej 44</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">2123847</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="H2">
+      <c r="J2">
         <v>2511</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -156,53 +176,63 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Herstedvestervej 46</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">2123847</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>3972</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -221,53 +251,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Herstedvestervej 46</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">2123847</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>2312</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -286,53 +326,63 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Herstedvestervej 52</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">2123847</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="H5">
+      <c r="J5">
         <v>829</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -351,53 +401,63 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Hjortens Kvt 9</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve">100044537</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H6">
+      <c r="J6">
         <v>1100</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -416,53 +476,63 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Holsbjergvej 44</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t xml:space="preserve">2125234</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>2763</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,53 +551,63 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Holsbjergvej 44</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t xml:space="preserve">2125234</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>405</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -546,53 +626,63 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Liljens Kvt 2</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t xml:space="preserve">100094947</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H9">
+      <c r="J9">
         <v>1968</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -611,53 +701,63 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Liljens Kvt 2</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t xml:space="preserve">100094947</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H10">
+      <c r="J10">
         <v>455</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -676,53 +776,63 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Løvens Kvt 17</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t xml:space="preserve">2125038</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="H11">
+      <c r="J11">
         <v>420</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -741,53 +851,63 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nordmarks Alle 1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t xml:space="preserve">8784860</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>1829</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -806,53 +926,63 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nyvej 5</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t xml:space="preserve">2125273</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H13">
+      <c r="J13">
         <v>1482</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -871,53 +1001,63 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nyvej 5</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t xml:space="preserve">2125273</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H14">
+      <c r="J14">
         <v>618</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -936,53 +1076,63 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Oksens Kvt 12</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t xml:space="preserve">2124951</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>1582</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1001,53 +1151,63 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Skallerne 14</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t xml:space="preserve">8784818</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H16">
+      <c r="J16">
         <v>674</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1066,53 +1226,63 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Snubbekorsvej 52</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t xml:space="preserve">9923612, 100724817</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H17">
+      <c r="J17">
         <v>318</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1131,53 +1301,63 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Snubbekorsvej 54</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t xml:space="preserve">9923612, 100724818</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H18">
+      <c r="J18">
         <v>275</v>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1196,53 +1376,63 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Stationsporten 6</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t xml:space="preserve">225981, 225982</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H19">
+      <c r="J19">
         <v>13898</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1261,53 +1451,63 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Stationstorvet 14</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t xml:space="preserve">100060976</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="H20">
+      <c r="J20">
         <v>1371</v>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1326,53 +1526,63 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Vognporten 1</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t xml:space="preserve">100094947</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="H21">
+      <c r="J21">
         <v>560</v>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1391,53 +1601,63 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Vognporten 6</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t xml:space="preserve">2124991</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H22">
+      <c r="J22">
         <v>613</v>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1456,53 +1676,63 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nyvej 5</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t xml:space="preserve">2125273</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="H23">
+      <c r="J23">
         <v>2025</v>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t xml:space="preserve">200028407</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">COWI A/S (Kongens Lyngby)</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-02-23</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1521,53 +1751,63 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nyvej 13</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t xml:space="preserve">2125273</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="H24">
+      <c r="J24">
         <v>7259</v>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t xml:space="preserve">200045323</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-02-07</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1586,53 +1826,63 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nyvej 5</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t xml:space="preserve">2125273</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H25">
+      <c r="J25">
         <v>1049</v>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t xml:space="preserve">200045323</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-02-07</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1651,53 +1901,63 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nyvej 5</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t xml:space="preserve">2125273</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="H26">
+      <c r="J26">
         <v>2072</v>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t xml:space="preserve">200045323</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-02-07</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1716,53 +1976,63 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nyvej 5</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t xml:space="preserve">2125273</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="H27">
+      <c r="J27">
         <v>1182</v>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t xml:space="preserve">200045323</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-02-07</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1781,53 +2051,63 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Herstedvestervej 44</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t xml:space="preserve">2123847</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H28">
+      <c r="J28">
         <v>4250</v>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t xml:space="preserve">200046187</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-02-28</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1846,53 +2126,63 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Skallerne 14</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t xml:space="preserve">8784818</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H29">
+      <c r="J29">
         <v>3270</v>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t xml:space="preserve">200048121</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-04-15</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1911,53 +2201,63 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gymnasievej 1</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t xml:space="preserve">2124986</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H30">
+      <c r="J30">
         <v>5983</v>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t xml:space="preserve">200049534</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-05-25</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1976,53 +2276,63 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bibliotekstorvet 1</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">8784860</t>
+          <t xml:space="preserve">Vridsløsestræde 23A</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H31">
-        <v>8794</v>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7831254</t>
+        </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054024</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+          <t xml:space="preserve">22</t>
+        </is>
+      </c>
+      <c r="J31">
+        <v>809</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200049581</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2021-10-19</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021-05-26</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2041,53 +2351,63 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordmarks Alle 1</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">8784860</t>
+          <t xml:space="preserve">Vridsløsestræde 29</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="H32">
-        <v>5846</v>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7831254</t>
+        </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054020</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+          <t xml:space="preserve">16</t>
+        </is>
+      </c>
+      <c r="J32">
+        <v>516</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200049581</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2021-10-19</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021-05-26</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2106,53 +2426,63 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyvej 9</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2125273</t>
+          <t xml:space="preserve">Vridsløsestræde 31</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
-        </is>
-      </c>
-      <c r="H33">
-        <v>4067</v>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7831254</t>
+        </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054014</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c r="J33">
+        <v>575</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200049581</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2021-10-19</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021-05-26</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2171,53 +2501,63 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egelundsvej 6C</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2124457</t>
+          <t xml:space="preserve">Bibliotekstorvet 1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8784860</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H34">
-        <v>1100</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310021743</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FORCE Technology</t>
-        </is>
+      <c r="J34">
+        <v>8794</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-01-23</t>
+          <t xml:space="preserve">200054024</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021-10-19</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2236,53 +2576,63 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gamle Landevej 47B</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">100022738</t>
+          <t xml:space="preserve">Gamle Landevej 25A</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2126191</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H35">
-        <v>1100</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310021739</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FORCE Technology</t>
-        </is>
+      <c r="J35">
+        <v>2404</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-01-23</t>
+          <t xml:space="preserve">200054016</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021-10-19</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2301,53 +2651,63 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rypehusene 3</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">713616, 2123223</t>
+          <t xml:space="preserve">Nordmarks Alle 1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8784860</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H36">
-        <v>1381</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311028814</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Orbicon A/S</t>
-        </is>
+      <c r="J36">
+        <v>5846</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-11-27</t>
+          <t xml:space="preserve">200054020</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021-10-19</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2366,53 +2726,63 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egelundsvej 6A</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2124867</t>
+          <t xml:space="preserve">Nyvej 9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H37">
-        <v>678</v>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2125273</t>
+        </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311148856</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FORCE Technology</t>
-        </is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="J37">
+        <v>4067</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-04</t>
+          <t xml:space="preserve">200054014</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021-10-19</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2431,53 +2801,63 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egelundsvej 6E</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2124459</t>
+          <t xml:space="preserve">Egelundsvej 6C</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2124457</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H38">
-        <v>430</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311148857</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38">
+        <v>1100</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">310021743</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">FORCE Technology</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-04</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023-01-23</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2496,53 +2876,63 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egelundsvej 7</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2124868</t>
+          <t xml:space="preserve">Gamle Landevej 47B</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100022738</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H39">
-        <v>400</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311148858</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="J39">
+        <v>1100</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">310021739</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">FORCE Technology</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-04</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023-01-23</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2561,53 +2951,63 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egelundsvej 7C</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2124456</t>
+          <t xml:space="preserve">Rypehusene 3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H40">
-        <v>679</v>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">713616, 2123223</t>
+        </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311148859</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FORCE Technology</t>
-        </is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J40">
+        <v>1381</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-04</t>
+          <t xml:space="preserve">311028814</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023-11-27</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2626,53 +3026,63 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roholmsvej 22</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2126175</t>
+          <t xml:space="preserve">Egelundsvej 6A</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2124867</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H41">
-        <v>289</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311148851</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="J41">
+        <v>678</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311148856</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">FORCE Technology</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-12-04</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2691,53 +3101,63 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stensmosevej 12</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">100061587</t>
+          <t xml:space="preserve">Egelundsvej 6E</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2124459</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H42">
-        <v>1115</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311148846</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="J42">
+        <v>430</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311148857</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">FORCE Technology</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-12-04</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2756,53 +3176,63 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gamle Landevej 47</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">8784819</t>
+          <t xml:space="preserve">Egelundsvej 7</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2124868</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H43">
-        <v>337</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311148948</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="J43">
+        <v>400</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311148858</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">FORCE Technology</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-06</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-04</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2821,53 +3251,63 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gamle Landevej 47</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">8784819</t>
+          <t xml:space="preserve">Egelundsvej 7C</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="H44">
-        <v>277</v>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2124456</t>
+        </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311148948</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J44">
+        <v>679</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311148859</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">FORCE Technology</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-06</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-04</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2886,53 +3326,63 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herstedvesterstræde 2</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2124150</t>
+          <t xml:space="preserve">Roholmsvej 22</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2126175</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H45">
-        <v>399</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311148952</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="J45">
+        <v>289</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311148851</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">FORCE Technology</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-06</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-04</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2951,53 +3401,63 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naverland 28</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2600</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2125729</t>
+          <t xml:space="preserve">Stensmosevej 12</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100061587</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H46">
-        <v>899</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311148950</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="J46">
+        <v>1115</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311148846</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">FORCE Technology</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-06</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-04</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3016,53 +3476,63 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rypehusene 15</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2123079</t>
+          <t xml:space="preserve">Gamle Landevej 47</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8784819</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H47">
-        <v>1233</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311148959</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="J47">
+        <v>337</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311148948</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">FORCE Technology</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-12-06</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3081,53 +3551,63 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vognporten 2</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2124997</t>
+          <t xml:space="preserve">Gamle Landevej 47</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H48">
-        <v>1136</v>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8784819</t>
+        </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311148964</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="J48">
+        <v>277</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311148948</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">FORCE Technology</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-12-06</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3146,53 +3626,63 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herstedvestervej 50</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2123847</t>
+          <t xml:space="preserve">Herstedvesterstræde 2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="H49">
-        <v>628</v>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2124150</t>
+        </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311150041</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J49">
+        <v>399</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311148952</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">FORCE Technology</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-14</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-06</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3211,53 +3701,63 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppelhusene 1</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naverland 28</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2600</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2127102</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2125729</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H50">
-        <v>352</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311150030</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="J50">
+        <v>899</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311148950</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">FORCE Technology</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-14</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-06</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3276,53 +3776,63 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vridsløsevej 1</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">8784871</t>
+          <t xml:space="preserve">Rypehusene 15</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
-        </is>
-      </c>
-      <c r="H51">
-        <v>346</v>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2123079</t>
+        </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311150635</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J51">
+        <v>1233</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311148959</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">FORCE Technology</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-17</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-06</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3341,53 +3851,63 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vridsløsestræde 23A</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">7831254</t>
+          <t xml:space="preserve">Vognporten 2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
-        </is>
-      </c>
-      <c r="H52">
-        <v>809</v>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2124997</t>
+        </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311155950</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J52">
+        <v>1136</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311148964</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">FORCE Technology</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-28</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-06</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3406,53 +3926,63 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vridsløsestræde 29</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">7831254</t>
+          <t xml:space="preserve">Gamle Landevej 27</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
-        </is>
-      </c>
-      <c r="H53">
-        <v>516</v>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2126191</t>
+        </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311155950</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="J53">
+        <v>646</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311150036</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">FORCE Technology</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-28</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-14</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3471,53 +4001,63 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vridsløsestræde 31</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">7831254</t>
+          <t xml:space="preserve">Herstedvestervej 50</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
-        </is>
-      </c>
-      <c r="H54">
-        <v>575</v>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2123847</t>
+        </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311155950</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="J54">
+        <v>628</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311150041</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">FORCE Technology</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-28</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-14</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3536,53 +4076,63 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gamle Landevej 15</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2125863</t>
+          <t xml:space="preserve">Poppelhusene 1</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2127102</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H55">
-        <v>1679</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311160628</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
+      <c r="J55">
+        <v>352</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311150030</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">FORCE Technology</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-02-24</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-14</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3601,55 +4151,65 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vognporten 10</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">100060976</t>
+          <t xml:space="preserve">Vridsløsevej 1</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H56">
-        <v>7682</v>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8784871</t>
+        </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723108</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Højbjerg Energimærkning</t>
-        </is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
+      <c r="J56">
+        <v>346</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-17</t>
+          <t xml:space="preserve">311150635</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">FORCE Technology</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">2025-12-17</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -3666,55 +4226,65 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Damgårdsvej 10</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2122816</t>
+          <t xml:space="preserve">Gamle Landevej 15</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2125863</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H57">
-        <v>293</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311794650</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tæthedskompagniet ApS</t>
-        </is>
+      <c r="J57">
+        <v>1679</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-31</t>
+          <t xml:space="preserve">311160628</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">FORCE Technology</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">2026-02-24</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -3731,53 +4301,63 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egelundsvej 8</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2122391</t>
+          <t xml:space="preserve">Bymosevej 2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2125572</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H58">
-        <v>7679</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311871259</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
-        </is>
+      <c r="J58">
+        <v>306</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-02</t>
+          <t xml:space="preserve">311630294</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2032-09-23</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3796,53 +4376,63 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gamle Landevej 25A</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2126191</t>
+          <t xml:space="preserve">Vognporten 10</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100060976</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H59">
-        <v>2404</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311871256</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="J59">
+        <v>7682</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-02</t>
+          <t xml:space="preserve">311723108</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Højbjerg Energimærkning</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2033-11-17</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3861,53 +4451,63 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gamle Landevej 27</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2126191</t>
+          <t xml:space="preserve">Damgårdsvej 10</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
-        </is>
-      </c>
-      <c r="H60">
-        <v>646</v>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2122816</t>
+        </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871256</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J60">
+        <v>293</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-02</t>
+          <t xml:space="preserve">311794650</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tæthedskompagniet ApS</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2034-10-31</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3926,53 +4526,63 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trippendalsvej 2</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2126191</t>
+          <t xml:space="preserve">Egelundsvej 8</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
-        </is>
-      </c>
-      <c r="H61">
-        <v>12126</v>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2122391</t>
+        </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871256</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J61">
+        <v>7679</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
+          <t xml:space="preserve">311871259</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-02</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3991,53 +4601,63 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t xml:space="preserve">Trippendalsvej 2</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
         <is>
           <t xml:space="preserve">2126191</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8</t>
-        </is>
-      </c>
-      <c r="H62">
-        <v>1759</v>
-      </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871256</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="J62">
+        <v>12126</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
+          <t xml:space="preserve">311871258</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-02</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4056,53 +4676,63 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herstedvesterstræde 2</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2124150</t>
+          <t xml:space="preserve">Trippendalsvej 2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="H63">
-        <v>422</v>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2126191</t>
+        </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878847</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
-        </is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="J63">
+        <v>1759</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-27</t>
+          <t xml:space="preserve">311871257</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2035-12-02</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4121,53 +4751,63 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topperne 8B</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2123854</t>
+          <t xml:space="preserve">Herstedvesterstræde 2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H64">
-        <v>407</v>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2124150</t>
+        </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883977</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
-        </is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="J64">
+        <v>422</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-25</t>
+          <t xml:space="preserve">311878847</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2036-01-27</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4186,53 +4826,63 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Løvens Kvt 17</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2125038</t>
+          <t xml:space="preserve">Topperne 8B</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="H65">
-        <v>2970</v>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2123854</t>
+        </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311901023</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J65">
+        <v>407</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311883977</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2036-05-13</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2036-02-25</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4251,53 +4901,63 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oksens Kvt 14</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Løvens Kvt 17</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2125038</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="H66">
-        <v>3461</v>
-      </c>
       <c r="I66" t="inlineStr">
         <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="J66">
+        <v>2970</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">311901023</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-13</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4316,53 +4976,63 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t xml:space="preserve">Oksens Kvt 14</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
         <is>
           <t xml:space="preserve">2125038</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="H67">
-        <v>1704</v>
-      </c>
       <c r="I67" t="inlineStr">
         <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J67">
+        <v>3461</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">311901023</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-13</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4381,53 +5051,63 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bymosevej 2</t>
+          <t xml:space="preserve">Albertslund Kommune</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">165</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2125572</t>
+          <t xml:space="preserve">Oksens Kvt 14</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H68">
-        <v>306</v>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2125038</t>
+        </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311902930</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="J68">
+        <v>1704</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311901023</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2036-05-21</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2036-05-13</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4446,53 +5126,63 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t xml:space="preserve">Damgårdsvej 12</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
         <is>
           <t xml:space="preserve">2122811</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H69">
+      <c r="J69">
         <v>874</v>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t xml:space="preserve">311902935</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4511,53 +5201,63 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t xml:space="preserve">Damgårdsvej 18</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
         <is>
           <t xml:space="preserve">2123836</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H70">
+      <c r="J70">
         <v>413</v>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t xml:space="preserve">311902926</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4576,53 +5276,63 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t xml:space="preserve">Damgårdsvej 18</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
         <is>
           <t xml:space="preserve">2123836</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H71">
+      <c r="J71">
         <v>358</v>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t xml:space="preserve">311902926</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4641,53 +5351,63 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t xml:space="preserve">Damgårdsvej 20</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
         <is>
           <t xml:space="preserve">2123836</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H72">
+      <c r="J72">
         <v>413</v>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t xml:space="preserve">311902926</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4706,53 +5426,63 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t xml:space="preserve">Damgårdsvej 22</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
         <is>
           <t xml:space="preserve">2123836</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="H73">
+      <c r="J73">
         <v>482</v>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t xml:space="preserve">311902926</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4771,53 +5501,63 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t xml:space="preserve">Damgårdsvej 25</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
         <is>
           <t xml:space="preserve">2123837</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H74">
+      <c r="J74">
         <v>317</v>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t xml:space="preserve">311902922</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4836,53 +5576,63 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t xml:space="preserve">Damgårdsvej 25</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
         <is>
           <t xml:space="preserve">2123837</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H75">
+      <c r="J75">
         <v>919</v>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t xml:space="preserve">311902923</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4901,53 +5651,63 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t xml:space="preserve">Degnehusene 113</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
         <is>
           <t xml:space="preserve">2126283</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H76">
+      <c r="J76">
         <v>360</v>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t xml:space="preserve">311902938</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4966,53 +5726,63 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t xml:space="preserve">Degnehusene 115</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
         <is>
           <t xml:space="preserve">2126283</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H77">
+      <c r="J77">
         <v>360</v>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t xml:space="preserve">311902937</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5031,53 +5801,63 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t xml:space="preserve">Degnehusene 117</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
         <is>
           <t xml:space="preserve">2126284</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H78">
+      <c r="J78">
         <v>360</v>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t xml:space="preserve">311902881</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5096,53 +5876,63 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t xml:space="preserve">Degnehusene 53</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
+      <c r="G79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
         <is>
           <t xml:space="preserve">2126282</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H79">
+      <c r="J79">
         <v>444</v>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t xml:space="preserve">311902877</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5161,53 +5951,63 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t xml:space="preserve">Egelundsvej 9</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
+      <c r="G80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
         <is>
           <t xml:space="preserve">2124876</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H80">
+      <c r="J80">
         <v>669</v>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t xml:space="preserve">311902883</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5226,53 +6026,63 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t xml:space="preserve">Galgebakken Torv 202</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
         <is>
           <t xml:space="preserve">9001502</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H81">
+      <c r="J81">
         <v>1038</v>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t xml:space="preserve">311902880</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5291,53 +6101,63 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t xml:space="preserve">Humlehusene 1A</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
+      <c r="G82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
         <is>
           <t xml:space="preserve">8088753</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H82">
+      <c r="J82">
         <v>500</v>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t xml:space="preserve">311902933</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5356,53 +6176,63 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t xml:space="preserve">Humlehusene 1B</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
+      <c r="G83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
         <is>
           <t xml:space="preserve">8088753</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H83">
+      <c r="J83">
         <v>500</v>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t xml:space="preserve">311902933</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5421,53 +6251,63 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t xml:space="preserve">Humlehusene 1C</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
+      <c r="G84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
         <is>
           <t xml:space="preserve">8088753</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H84">
+      <c r="J84">
         <v>500</v>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t xml:space="preserve">311902933</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5486,53 +6326,63 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t xml:space="preserve">Humlehusene 3</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
+      <c r="G85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
         <is>
           <t xml:space="preserve">8088755</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H85">
+      <c r="J85">
         <v>766</v>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t xml:space="preserve">311902879</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5551,53 +6401,63 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t xml:space="preserve">Humlehusene 5</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
+      <c r="G86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
         <is>
           <t xml:space="preserve">8088754</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H86">
+      <c r="J86">
         <v>465</v>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="K86" t="inlineStr">
         <is>
           <t xml:space="preserve">311902878</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5616,53 +6476,63 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t xml:space="preserve">Humlehusene 7D</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
+      <c r="G87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
         <is>
           <t xml:space="preserve">2125992</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H87">
+      <c r="J87">
         <v>2011</v>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t xml:space="preserve">311902882</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="N87" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="O87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5681,53 +6551,63 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t xml:space="preserve">Løvens Kvt 17</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
+      <c r="G88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
         <is>
           <t xml:space="preserve">2125038</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="H88">
+      <c r="J88">
         <v>1001</v>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="K88" t="inlineStr">
         <is>
           <t xml:space="preserve">311902940</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="N88" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="O88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5746,53 +6626,63 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t xml:space="preserve">Storetorv 40</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
+      <c r="G89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
         <is>
           <t xml:space="preserve">2123826</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H89">
+      <c r="J89">
         <v>799</v>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t xml:space="preserve">311902920</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="N89" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="O89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5811,53 +6701,63 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tranehusene 75</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
+      <c r="G90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
         <is>
           <t xml:space="preserve">8784834</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H90">
+      <c r="J90">
         <v>672</v>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t xml:space="preserve">311904834</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t xml:space="preserve">ISOLINK ApS</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-30</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="O90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5876,53 +6776,63 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tranehusene 75</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
+      <c r="G91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
         <is>
           <t xml:space="preserve">8784834</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="H91">
+      <c r="J91">
         <v>348</v>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t xml:space="preserve">311904834</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t xml:space="preserve">ISOLINK ApS</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-30</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="N91" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="O91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5941,59 +6851,69 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">165</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Albertslund Kommune</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tranehusene 77</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
+      <c r="G92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2620</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
         <is>
           <t xml:space="preserve">8784834</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="H92">
+      <c r="J92">
         <v>887</v>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="K92" t="inlineStr">
         <is>
           <t xml:space="preserve">311904834</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t xml:space="preserve">ISOLINK ApS</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-30</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="N92" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr">
+      <c r="O92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M92"/>
+  <autoFilter ref="A1:O92"/>
 </worksheet>
 </file>
--- a/public/exports/66137112.xlsx
+++ b/public/exports/66137112.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311148948</t>
+          <t xml:space="preserve">311148949</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">

--- a/public/exports/66137112.xlsx
+++ b/public/exports/66137112.xlsx
@@ -3514,7 +3514,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311148949</t>
+          <t xml:space="preserve">311148948</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
